--- a/Deliverables/BOM/ARC_1.0.5/PCBWay-BOM.xlsx
+++ b/Deliverables/BOM/ARC_1.0.5/PCBWay-BOM.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="438">
   <si>
     <t>Component list</t>
   </si>
@@ -1330,6 +1330,9 @@
   </si>
   <si>
     <t>MC78M05BDTRKG</t>
+  </si>
+  <si>
+    <t>Do Not MOUNT</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1342,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1476,6 +1479,14 @@
       <b/>
       <strike/>
       <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1700,7 +1711,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1813,15 +1824,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1857,6 +1859,21 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2227,11 +2244,11 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
-      <c r="L1" s="46"/>
-      <c r="M1" s="46"/>
-      <c r="N1" s="46"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
     </row>
     <row r="2" spans="1:14" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2271,7 +2288,7 @@
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="47"/>
+      <c r="N3" s="59"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2291,7 +2308,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
       <c r="M4" s="6"/>
-      <c r="N4" s="48"/>
+      <c r="N4" s="60"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2311,7 +2328,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5"/>
-      <c r="N5" s="48"/>
+      <c r="N5" s="60"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2327,7 +2344,7 @@
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="48"/>
+      <c r="N6" s="60"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2343,7 +2360,7 @@
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
-      <c r="N7" s="48"/>
+      <c r="N7" s="60"/>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2359,7 +2376,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
       <c r="M8" s="7"/>
-      <c r="N8" s="48"/>
+      <c r="N8" s="60"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2409,7 +2426,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="49" t="s">
+      <c r="C10" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D10" s="29" t="s">
@@ -2451,7 +2468,7 @@
         <f t="shared" ref="B11:B84" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D11" s="31" t="s">
@@ -2493,7 +2510,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D12" s="29" t="s">
@@ -2535,7 +2552,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="50" t="s">
+      <c r="C13" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D13" s="31" t="s">
@@ -2577,7 +2594,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="49" t="s">
+      <c r="C14" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D14" s="29" t="s">
@@ -2619,7 +2636,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="50" t="s">
+      <c r="C15" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D15" s="31" t="s">
@@ -2661,7 +2678,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D16" s="29" t="s">
@@ -2703,7 +2720,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D17" s="31" t="s">
@@ -2745,7 +2762,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D18" s="29" t="s">
@@ -2787,7 +2804,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C19" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D19" s="31" t="s">
@@ -2829,7 +2846,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D20" s="29" t="s">
@@ -2871,7 +2888,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D21" s="31" t="s">
@@ -2913,7 +2930,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="46" t="s">
         <v>341</v>
       </c>
       <c r="D22" s="29" t="s">
@@ -2955,7 +2972,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="47" t="s">
         <v>341</v>
       </c>
       <c r="D23" s="31" t="s">
@@ -2997,7 +3014,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="46" t="s">
         <v>345</v>
       </c>
       <c r="D24" s="29" t="s">
@@ -3039,7 +3056,7 @@
         <f>ROW(B25) - ROW($B$9)</f>
         <v>16</v>
       </c>
-      <c r="C25" s="50" t="s">
+      <c r="C25" s="47" t="s">
         <v>345</v>
       </c>
       <c r="D25" s="31" t="s">
@@ -3081,7 +3098,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="46" t="s">
         <v>345</v>
       </c>
       <c r="D26" s="29" t="s">
@@ -3123,7 +3140,7 @@
         <f>ROW(B27) - ROW($B$9)</f>
         <v>18</v>
       </c>
-      <c r="C27" s="50" t="s">
+      <c r="C27" s="47" t="s">
         <v>345</v>
       </c>
       <c r="D27" s="31" t="s">
@@ -3165,7 +3182,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="C28" s="49" t="s">
+      <c r="C28" s="46" t="s">
         <v>345</v>
       </c>
       <c r="D28" s="29" t="s">
@@ -3207,7 +3224,7 @@
         <f>ROW(B29) - ROW($B$9)</f>
         <v>20</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="47" t="s">
         <v>345</v>
       </c>
       <c r="D29" s="31" t="s">
@@ -3249,7 +3266,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="C30" s="49" t="s">
+      <c r="C30" s="46" t="s">
         <v>345</v>
       </c>
       <c r="D30" s="29" t="s">
@@ -3291,41 +3308,43 @@
         <f>ROW(B31) - ROW($B$9)</f>
         <v>22</v>
       </c>
-      <c r="C31" s="50" t="s">
+      <c r="C31" s="47" t="s">
         <v>346</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="F31" s="31" t="s">
+      <c r="F31" s="49" t="s">
         <v>342</v>
       </c>
-      <c r="G31" s="31" t="s">
+      <c r="G31" s="49" t="s">
         <v>428</v>
       </c>
-      <c r="H31" s="31" t="s">
+      <c r="H31" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="I31" s="31" t="s">
+      <c r="I31" s="49" t="s">
         <v>386</v>
       </c>
-      <c r="J31" s="31" t="s">
+      <c r="J31" s="49" t="s">
         <v>353</v>
       </c>
-      <c r="K31" s="32">
+      <c r="K31" s="53">
         <v>1</v>
       </c>
-      <c r="L31" s="31">
+      <c r="L31" s="49">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M31" s="31">
+      <c r="M31" s="49">
         <v>10</v>
       </c>
-      <c r="N31" s="34"/>
+      <c r="N31" s="61" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
@@ -3333,41 +3352,43 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="C32" s="49" t="s">
+      <c r="C32" s="46" t="s">
         <v>346</v>
       </c>
-      <c r="D32" s="29" t="s">
+      <c r="D32" s="51" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="48" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="29" t="s">
+      <c r="F32" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="51" t="s">
         <v>429</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H32" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="I32" s="29" t="s">
+      <c r="I32" s="51" t="s">
         <v>387</v>
       </c>
-      <c r="J32" s="29" t="s">
+      <c r="J32" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K32" s="30">
+      <c r="K32" s="48">
         <v>1</v>
       </c>
-      <c r="L32" s="29">
+      <c r="L32" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M32" s="29">
+      <c r="M32" s="51">
         <v>10</v>
       </c>
-      <c r="N32" s="33"/>
+      <c r="N32" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3375,7 +3396,7 @@
         <f>ROW(B33) - ROW($B$9)</f>
         <v>24</v>
       </c>
-      <c r="C33" s="50" t="s">
+      <c r="C33" s="47" t="s">
         <v>347</v>
       </c>
       <c r="D33" s="31" t="s">
@@ -3417,41 +3438,43 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C34" s="49" t="s">
+      <c r="C34" s="46" t="s">
         <v>348</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="30" t="s">
+      <c r="E34" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="G34" s="30" t="s">
+      <c r="G34" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="H34" s="29" t="s">
+      <c r="H34" s="51" t="s">
         <v>258</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="51" t="s">
         <v>388</v>
       </c>
-      <c r="J34" s="29" t="s">
+      <c r="J34" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K34" s="30">
+      <c r="K34" s="48">
         <v>1</v>
       </c>
-      <c r="L34" s="29">
+      <c r="L34" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M34" s="29">
+      <c r="M34" s="51">
         <v>10</v>
       </c>
-      <c r="N34" s="33"/>
+      <c r="N34" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
@@ -3459,7 +3482,7 @@
         <f>ROW(B35) - ROW($B$9)</f>
         <v>26</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="47" t="s">
         <v>349</v>
       </c>
       <c r="D35" s="31" t="s">
@@ -3501,7 +3524,7 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="C36" s="49" t="s">
+      <c r="C36" s="46" t="s">
         <v>349</v>
       </c>
       <c r="D36" s="29" t="s">
@@ -3543,7 +3566,7 @@
         <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="50" t="s">
+      <c r="C37" s="47" t="s">
         <v>349</v>
       </c>
       <c r="D37" s="31" t="s">
@@ -3585,7 +3608,7 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="49" t="s">
+      <c r="C38" s="46" t="s">
         <v>350</v>
       </c>
       <c r="D38" s="29" t="s">
@@ -3627,7 +3650,7 @@
         <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="47" t="s">
         <v>350</v>
       </c>
       <c r="D39" s="31" t="s">
@@ -3669,7 +3692,7 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="49" t="s">
+      <c r="C40" s="46" t="s">
         <v>351</v>
       </c>
       <c r="D40" s="29" t="s">
@@ -3711,41 +3734,43 @@
         <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="50" t="s">
+      <c r="C41" s="47" t="s">
         <v>352</v>
       </c>
-      <c r="D41" s="31" t="s">
+      <c r="D41" s="51" t="s">
         <v>37</v>
       </c>
-      <c r="E41" s="32" t="s">
+      <c r="E41" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="F41" s="31" t="s">
+      <c r="F41" s="51" t="s">
         <v>170</v>
       </c>
-      <c r="G41" s="31" t="s">
+      <c r="G41" s="51" t="s">
         <v>432</v>
       </c>
-      <c r="H41" s="31" t="s">
+      <c r="H41" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="I41" s="31" t="s">
+      <c r="I41" s="51" t="s">
         <v>395</v>
       </c>
-      <c r="J41" s="31" t="s">
+      <c r="J41" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="48">
         <v>1</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="51">
         <v>20</v>
       </c>
-      <c r="N41" s="34"/>
+      <c r="N41" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
@@ -3753,41 +3778,43 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="49" t="s">
+      <c r="C42" s="46" t="s">
         <v>348</v>
       </c>
-      <c r="D42" s="29" t="s">
+      <c r="D42" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="E42" s="30" t="s">
+      <c r="E42" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="29" t="s">
+      <c r="F42" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="G42" s="30" t="s">
+      <c r="G42" s="51" t="s">
         <v>171</v>
       </c>
-      <c r="H42" s="29" t="s">
+      <c r="H42" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="I42" s="29" t="s">
+      <c r="I42" s="51" t="s">
         <v>396</v>
       </c>
-      <c r="J42" s="29" t="s">
+      <c r="J42" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K42" s="30">
+      <c r="K42" s="48">
         <v>1</v>
       </c>
-      <c r="L42" s="29">
+      <c r="L42" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M42" s="29">
+      <c r="M42" s="51">
         <v>10</v>
       </c>
-      <c r="N42" s="33"/>
+      <c r="N42" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
@@ -3795,41 +3822,43 @@
         <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="47" t="s">
         <v>352</v>
       </c>
-      <c r="D43" s="31" t="s">
+      <c r="D43" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="F43" s="31" t="s">
+      <c r="F43" s="51" t="s">
         <v>172</v>
       </c>
-      <c r="G43" s="31" t="s">
+      <c r="G43" s="51" t="s">
         <v>433</v>
       </c>
-      <c r="H43" s="31" t="s">
+      <c r="H43" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="I43" s="31" t="s">
+      <c r="I43" s="51" t="s">
         <v>397</v>
       </c>
-      <c r="J43" s="31" t="s">
+      <c r="J43" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K43" s="32">
+      <c r="K43" s="48">
         <v>1</v>
       </c>
-      <c r="L43" s="31">
+      <c r="L43" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M43" s="31">
+      <c r="M43" s="51">
         <v>20</v>
       </c>
-      <c r="N43" s="34"/>
+      <c r="N43" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
@@ -3837,41 +3866,43 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="53" t="s">
+      <c r="C44" s="50" t="s">
         <v>315</v>
       </c>
-      <c r="D44" s="54" t="s">
+      <c r="D44" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="E44" s="51" t="s">
+      <c r="E44" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="F44" s="54" t="s">
+      <c r="F44" s="51" t="s">
         <v>173</v>
       </c>
-      <c r="G44" s="51" t="s">
+      <c r="G44" s="48" t="s">
         <v>353</v>
       </c>
-      <c r="H44" s="54" t="s">
+      <c r="H44" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="I44" s="54" t="s">
+      <c r="I44" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="J44" s="54" t="s">
+      <c r="J44" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K44" s="51">
+      <c r="K44" s="48">
         <v>2</v>
       </c>
-      <c r="L44" s="54">
+      <c r="L44" s="51">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="M44" s="51" t="s">
+      <c r="M44" s="48" t="s">
         <v>353</v>
       </c>
-      <c r="N44" s="33"/>
+      <c r="N44" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
@@ -3879,7 +3910,7 @@
         <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="50" t="s">
+      <c r="C45" s="47" t="s">
         <v>354</v>
       </c>
       <c r="D45" s="31" t="s">
@@ -3921,7 +3952,7 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="49" t="s">
+      <c r="C46" s="46" t="s">
         <v>354</v>
       </c>
       <c r="D46" s="29" t="s">
@@ -3963,7 +3994,7 @@
         <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="47" t="s">
         <v>354</v>
       </c>
       <c r="D47" s="31" t="s">
@@ -4005,7 +4036,7 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="49" t="s">
+      <c r="C48" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D48" s="29" t="s">
@@ -4047,7 +4078,7 @@
         <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D49" s="31" t="s">
@@ -4089,7 +4120,7 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="C50" s="49" t="s">
+      <c r="C50" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D50" s="29" t="s">
@@ -4131,7 +4162,7 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="C51" s="50" t="s">
+      <c r="C51" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D51" s="31" t="s">
@@ -4173,7 +4204,7 @@
         <f>ROW(B52) - ROW($B$9)</f>
         <v>43</v>
       </c>
-      <c r="C52" s="49" t="s">
+      <c r="C52" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D52" s="29" t="s">
@@ -4215,7 +4246,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="C53" s="50" t="s">
+      <c r="C53" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D53" s="31" t="s">
@@ -4257,7 +4288,7 @@
         <f>ROW(B54) - ROW($B$9)</f>
         <v>45</v>
       </c>
-      <c r="C54" s="49" t="s">
+      <c r="C54" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D54" s="29" t="s">
@@ -4299,7 +4330,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="C55" s="50" t="s">
+      <c r="C55" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D55" s="31" t="s">
@@ -4341,7 +4372,7 @@
         <f>ROW(B56) - ROW($B$9)</f>
         <v>47</v>
       </c>
-      <c r="C56" s="49" t="s">
+      <c r="C56" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D56" s="29" t="s">
@@ -4383,7 +4414,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="C57" s="50" t="s">
+      <c r="C57" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D57" s="31" t="s">
@@ -4425,7 +4456,7 @@
         <f>ROW(B58) - ROW($B$9)</f>
         <v>49</v>
       </c>
-      <c r="C58" s="49" t="s">
+      <c r="C58" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D58" s="29" t="s">
@@ -4467,7 +4498,7 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="C59" s="50" t="s">
+      <c r="C59" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D59" s="31" t="s">
@@ -4509,7 +4540,7 @@
         <f>ROW(B60) - ROW($B$9)</f>
         <v>51</v>
       </c>
-      <c r="C60" s="49" t="s">
+      <c r="C60" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D60" s="29" t="s">
@@ -4551,7 +4582,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="C61" s="50" t="s">
+      <c r="C61" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D61" s="31" t="s">
@@ -4593,7 +4624,7 @@
         <f>ROW(B62) - ROW($B$9)</f>
         <v>53</v>
       </c>
-      <c r="C62" s="49" t="s">
+      <c r="C62" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D62" s="29" t="s">
@@ -4635,7 +4666,7 @@
         <f>ROW(B63) - ROW($B$9)</f>
         <v>54</v>
       </c>
-      <c r="C63" s="50" t="s">
+      <c r="C63" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D63" s="31" t="s">
@@ -4677,7 +4708,7 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="C64" s="49" t="s">
+      <c r="C64" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D64" s="29" t="s">
@@ -4719,7 +4750,7 @@
         <f>ROW(B65) - ROW($B$9)</f>
         <v>56</v>
       </c>
-      <c r="C65" s="50" t="s">
+      <c r="C65" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D65" s="31" t="s">
@@ -4761,7 +4792,7 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="C66" s="49" t="s">
+      <c r="C66" s="46" t="s">
         <v>272</v>
       </c>
       <c r="D66" s="29" t="s">
@@ -4803,7 +4834,7 @@
         <f>ROW(B67) - ROW($B$9)</f>
         <v>58</v>
       </c>
-      <c r="C67" s="50" t="s">
+      <c r="C67" s="47" t="s">
         <v>272</v>
       </c>
       <c r="D67" s="31" t="s">
@@ -4845,41 +4876,43 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="C68" s="49" t="s">
+      <c r="C68" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="51" t="s">
         <v>62</v>
       </c>
-      <c r="E68" s="30" t="s">
+      <c r="E68" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="G68" s="30" t="s">
+      <c r="G68" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="H68" s="29" t="s">
+      <c r="H68" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="51" t="s">
         <v>416</v>
       </c>
-      <c r="J68" s="29" t="s">
+      <c r="J68" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K68" s="30">
+      <c r="K68" s="48">
         <v>1</v>
       </c>
-      <c r="L68" s="29">
+      <c r="L68" s="51">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M68" s="29">
+      <c r="M68" s="51">
         <v>10</v>
       </c>
-      <c r="N68" s="33"/>
+      <c r="N68" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="69" spans="1:14" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
@@ -4887,38 +4920,38 @@
         <f>ROW(B69) - ROW($B$9)</f>
         <v>60</v>
       </c>
-      <c r="C69" s="55" t="s">
+      <c r="C69" s="52" t="s">
         <v>181</v>
       </c>
-      <c r="D69" s="52" t="s">
+      <c r="D69" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="E69" s="56" t="s">
+      <c r="E69" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="F69" s="52" t="s">
+      <c r="F69" s="49" t="s">
         <v>342</v>
       </c>
-      <c r="G69" s="52" t="s">
+      <c r="G69" s="49" t="s">
         <v>181</v>
       </c>
-      <c r="H69" s="52" t="s">
+      <c r="H69" s="49" t="s">
         <v>353</v>
       </c>
-      <c r="I69" s="52" t="s">
+      <c r="I69" s="49" t="s">
         <v>353</v>
       </c>
-      <c r="J69" s="52" t="s">
+      <c r="J69" s="49" t="s">
         <v>353</v>
       </c>
-      <c r="K69" s="56">
+      <c r="K69" s="53">
         <v>38</v>
       </c>
-      <c r="L69" s="52">
+      <c r="L69" s="49">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="M69" s="52" t="s">
+      <c r="M69" s="49" t="s">
         <v>353</v>
       </c>
       <c r="N69" s="34"/>
@@ -4929,7 +4962,7 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="C70" s="49" t="s">
+      <c r="C70" s="46" t="s">
         <v>359</v>
       </c>
       <c r="D70" s="29" t="s">
@@ -4971,7 +5004,7 @@
         <f>ROW(B71) - ROW($B$9)</f>
         <v>62</v>
       </c>
-      <c r="C71" s="50" t="s">
+      <c r="C71" s="47" t="s">
         <v>360</v>
       </c>
       <c r="D71" s="31" t="s">
@@ -5009,42 +5042,42 @@
     </row>
     <row r="72" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
-      <c r="B72" s="57">
+      <c r="B72" s="54">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="C72" s="58" t="s">
+      <c r="C72" s="55" t="s">
         <v>360</v>
       </c>
-      <c r="D72" s="59" t="s">
+      <c r="D72" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="E72" s="60" t="s">
+      <c r="E72" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="F72" s="59" t="s">
+      <c r="F72" s="56" t="s">
         <v>184</v>
       </c>
-      <c r="G72" s="60" t="s">
+      <c r="G72" s="57" t="s">
         <v>229</v>
       </c>
-      <c r="H72" s="59" t="s">
+      <c r="H72" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="I72" s="59" t="s">
+      <c r="I72" s="56" t="s">
         <v>353</v>
       </c>
-      <c r="J72" s="59" t="s">
+      <c r="J72" s="56" t="s">
         <v>353</v>
       </c>
-      <c r="K72" s="60">
+      <c r="K72" s="57">
         <v>1</v>
       </c>
-      <c r="L72" s="59">
+      <c r="L72" s="56">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="M72" s="59">
+      <c r="M72" s="56">
         <v>6</v>
       </c>
       <c r="N72" s="33"/>
@@ -5055,7 +5088,7 @@
         <f>ROW(B73) - ROW($B$9)</f>
         <v>64</v>
       </c>
-      <c r="C73" s="50" t="s">
+      <c r="C73" s="47" t="s">
         <v>360</v>
       </c>
       <c r="D73" s="31" t="s">
@@ -5097,7 +5130,7 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="C74" s="49" t="s">
+      <c r="C74" s="46" t="s">
         <v>360</v>
       </c>
       <c r="D74" s="29" t="s">
@@ -5139,7 +5172,7 @@
         <f>ROW(B75) - ROW($B$9)</f>
         <v>66</v>
       </c>
-      <c r="C75" s="50" t="s">
+      <c r="C75" s="47" t="s">
         <v>360</v>
       </c>
       <c r="D75" s="31" t="s">
@@ -5181,7 +5214,7 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="C76" s="49" t="s">
+      <c r="C76" s="46" t="s">
         <v>360</v>
       </c>
       <c r="D76" s="29" t="s">
@@ -5223,7 +5256,7 @@
         <f>ROW(B77) - ROW($B$9)</f>
         <v>68</v>
       </c>
-      <c r="C77" s="50" t="s">
+      <c r="C77" s="47" t="s">
         <v>360</v>
       </c>
       <c r="D77" s="31" t="s">
@@ -5265,7 +5298,7 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="C78" s="49" t="s">
+      <c r="C78" s="46" t="s">
         <v>360</v>
       </c>
       <c r="D78" s="29" t="s">
@@ -5307,41 +5340,43 @@
         <f>ROW(B79) - ROW($B$9)</f>
         <v>70</v>
       </c>
-      <c r="C79" s="50" t="s">
+      <c r="C79" s="47" t="s">
         <v>360</v>
       </c>
-      <c r="D79" s="31" t="s">
+      <c r="D79" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="E79" s="32" t="s">
+      <c r="E79" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="F79" s="31" t="s">
+      <c r="F79" s="49" t="s">
         <v>342</v>
       </c>
-      <c r="G79" s="31" t="s">
+      <c r="G79" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="H79" s="31" t="s">
+      <c r="H79" s="49" t="s">
         <v>282</v>
       </c>
-      <c r="I79" s="31" t="s">
+      <c r="I79" s="49" t="s">
         <v>424</v>
       </c>
-      <c r="J79" s="31" t="s">
+      <c r="J79" s="49" t="s">
         <v>353</v>
       </c>
-      <c r="K79" s="32">
+      <c r="K79" s="53">
         <v>1</v>
       </c>
-      <c r="L79" s="31">
+      <c r="L79" s="49">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M79" s="31">
+      <c r="M79" s="49">
         <v>6</v>
       </c>
-      <c r="N79" s="34"/>
+      <c r="N79" s="61" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="80" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
@@ -5349,41 +5384,43 @@
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="C80" s="49" t="s">
+      <c r="C80" s="46" t="s">
         <v>360</v>
       </c>
-      <c r="D80" s="29" t="s">
+      <c r="D80" s="51" t="s">
         <v>74</v>
       </c>
-      <c r="E80" s="30" t="s">
+      <c r="E80" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="F80" s="29" t="s">
+      <c r="F80" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="G80" s="30" t="s">
+      <c r="G80" s="48" t="s">
         <v>236</v>
       </c>
-      <c r="H80" s="29" t="s">
+      <c r="H80" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="I80" s="29" t="s">
+      <c r="I80" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="J80" s="29" t="s">
+      <c r="J80" s="51" t="s">
         <v>353</v>
       </c>
-      <c r="K80" s="30">
+      <c r="K80" s="48">
         <v>1</v>
       </c>
-      <c r="L80" s="29">
+      <c r="L80" s="51">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M80" s="29">
+      <c r="M80" s="51">
         <v>6</v>
       </c>
-      <c r="N80" s="33"/>
+      <c r="N80" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="81" spans="1:14" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
@@ -5391,7 +5428,7 @@
         <f>ROW(B81) - ROW($B$9)</f>
         <v>72</v>
       </c>
-      <c r="C81" s="50" t="s">
+      <c r="C81" s="47" t="s">
         <v>360</v>
       </c>
       <c r="D81" s="31" t="s">
@@ -5433,7 +5470,7 @@
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="C82" s="49" t="s">
+      <c r="C82" s="46" t="s">
         <v>360</v>
       </c>
       <c r="D82" s="29" t="s">
@@ -5475,7 +5512,7 @@
         <f>ROW(B83) - ROW($B$9)</f>
         <v>74</v>
       </c>
-      <c r="C83" s="50" t="s">
+      <c r="C83" s="47" t="s">
         <v>361</v>
       </c>
       <c r="D83" s="31" t="s">
@@ -5517,41 +5554,43 @@
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="C84" s="49" t="s">
+      <c r="C84" s="46" t="s">
         <v>361</v>
       </c>
-      <c r="D84" s="29" t="s">
+      <c r="D84" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="E84" s="30" t="s">
+      <c r="E84" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="F84" s="29" t="s">
+      <c r="F84" s="51" t="s">
         <v>342</v>
       </c>
-      <c r="G84" s="30" t="s">
+      <c r="G84" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="H84" s="29" t="s">
+      <c r="H84" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="I84" s="29" t="s">
+      <c r="I84" s="51" t="s">
         <v>296</v>
       </c>
-      <c r="J84" s="29" t="s">
+      <c r="J84" s="51" t="s">
         <v>336</v>
       </c>
-      <c r="K84" s="30">
+      <c r="K84" s="48">
         <v>1</v>
       </c>
-      <c r="L84" s="29">
+      <c r="L84" s="51">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="M84" s="29">
+      <c r="M84" s="51">
         <v>10</v>
       </c>
-      <c r="N84" s="33"/>
+      <c r="N84" s="62" t="s">
+        <v>437</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
